--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96705</v>
+        <v>96707</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96705</v>
+        <v>96707</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96597</v>
+        <v>96599</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135702883</v>
       </c>
       <c r="B5" t="n">
-        <v>96501</v>
+        <v>96503</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>135702899</v>
       </c>
       <c r="B6" t="n">
-        <v>99080</v>
+        <v>99082</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96707</v>
+        <v>96724</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96707</v>
+        <v>96724</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96599</v>
+        <v>96616</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135702883</v>
       </c>
       <c r="B5" t="n">
-        <v>96503</v>
+        <v>96520</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>135702899</v>
       </c>
       <c r="B6" t="n">
-        <v>99082</v>
+        <v>99099</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96724</v>
+        <v>96725</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96724</v>
+        <v>96725</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96616</v>
+        <v>96617</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135702883</v>
       </c>
       <c r="B5" t="n">
-        <v>96520</v>
+        <v>96521</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>135702899</v>
       </c>
       <c r="B6" t="n">
-        <v>99099</v>
+        <v>99100</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96725</v>
+        <v>96726</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96725</v>
+        <v>96726</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96617</v>
+        <v>96618</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135702883</v>
       </c>
       <c r="B5" t="n">
-        <v>96521</v>
+        <v>96522</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>135702899</v>
       </c>
       <c r="B6" t="n">
-        <v>99100</v>
+        <v>99101</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96726</v>
+        <v>96727</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96726</v>
+        <v>96727</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96618</v>
+        <v>96619</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135702883</v>
       </c>
       <c r="B5" t="n">
-        <v>96522</v>
+        <v>96523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>135702899</v>
       </c>
       <c r="B6" t="n">
-        <v>99101</v>
+        <v>99102</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96727</v>
+        <v>96733</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96619</v>
+        <v>96625</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135702883</v>
       </c>
       <c r="B5" t="n">
-        <v>96523</v>
+        <v>96529</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>135702899</v>
       </c>
       <c r="B6" t="n">
-        <v>99102</v>
+        <v>99108</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96733</v>
+        <v>96734</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96625</v>
+        <v>96626</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1029,7 +1029,7 @@
         <v>135702883</v>
       </c>
       <c r="B5" t="n">
-        <v>96529</v>
+        <v>96530</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1144,7 +1144,7 @@
         <v>135702899</v>
       </c>
       <c r="B6" t="n">
-        <v>99108</v>
+        <v>99109</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96734</v>
+        <v>96745</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96626</v>
+        <v>96637</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96745</v>
+        <v>96758</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96745</v>
+        <v>96758</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96637</v>
+        <v>96650</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96758</v>
+        <v>96759</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96650</v>
+        <v>96651</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96759</v>
+        <v>96772</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96651</v>
+        <v>96664</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 29056-2026 artfynd.xlsx
+++ b/artfynd/A 29056-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135702855</v>
       </c>
       <c r="B2" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -802,7 +802,7 @@
         <v>135702867</v>
       </c>
       <c r="B3" t="n">
-        <v>96772</v>
+        <v>96773</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -917,7 +917,7 @@
         <v>135702933</v>
       </c>
       <c r="B4" t="n">
-        <v>96664</v>
+        <v>96665</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
